--- a/datos_ciliopatias/KMO.xlsx
+++ b/datos_ciliopatias/KMO.xlsx
@@ -1,98 +1,88 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\crist\Desktop\TFM\TFM_R_proyect\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CC2700D-B3C1-4628-9623-0D7842D3D353}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
-  <si>
-    <t>KMO</t>
-  </si>
-  <si>
-    <t>Aural Anomalies</t>
-  </si>
-  <si>
-    <t>Cerebral Anomalies</t>
-  </si>
-  <si>
-    <t>Ciliopathy</t>
-  </si>
-  <si>
-    <t>Coronary and Vascular Anomalies</t>
-  </si>
-  <si>
-    <t>Digestive Anomalies</t>
-  </si>
-  <si>
-    <t>Facial Anomalies</t>
-  </si>
-  <si>
-    <t>Hormonal Anomalies</t>
-  </si>
-  <si>
-    <t>Liver Anomalies</t>
-  </si>
-  <si>
-    <t>Nasal Anomalies</t>
-  </si>
-  <si>
-    <t>Neural Anomalies</t>
-  </si>
-  <si>
-    <t>Ophthalmic Anomalies</t>
-  </si>
-  <si>
-    <t>Organ Anomalies</t>
-  </si>
-  <si>
-    <t>Others</t>
-  </si>
-  <si>
-    <t>Renal Anomalies</t>
-  </si>
-  <si>
-    <t>Reproductive Anomalies</t>
-  </si>
-  <si>
-    <t>Respiratory Anomalies</t>
-  </si>
-  <si>
-    <t>Skeletal Anomalies</t>
-  </si>
-  <si>
-    <t>Human.Gene.Name</t>
-  </si>
-  <si>
-    <t>Subcellular.Localization</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>Variable</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">KMO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aural Anomalies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cerebral Anomalies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ciliopathy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coronary and Vascular Anomalies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digestive Anomalies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Facial Anomalies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hormonal Anomalies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liver Anomalies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nasal Anomalies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neural Anomalies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ophthalmic Anomalies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Organ Anomalies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Others</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Renal Anomalies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reproductive Anomalies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Respiratory Anomalies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skeletal Anomalies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Human.Gene.Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subcellular.Localization</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -121,25 +111,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -421,183 +399,172 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="30.85546875" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1">
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="n">
         <v>0.47</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1">
+    <row r="3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="n">
         <v>0.46</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1">
+    <row r="4">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="n">
         <v>0.61</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1">
+    <row r="5">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="n">
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1">
+    <row r="6">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="n">
         <v>0.46</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1">
+    <row r="7">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" t="n">
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1">
+    <row r="8">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="n">
         <v>0.51</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1">
+    <row r="9">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" t="n">
         <v>0.66</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1">
+    <row r="10">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" t="n">
         <v>0.6</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1">
+    <row r="11">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" t="n">
         <v>0.67</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1">
+    <row r="12">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="n">
         <v>0.72</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" s="1">
+    <row r="13">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="n">
         <v>0.61</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="1">
+    <row r="14">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="n">
         <v>0.69</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="1">
+    <row r="15">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="n">
         <v>0.61</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" s="1">
+    <row r="16">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" t="n">
         <v>0.77</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" s="1">
+    <row r="17">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" t="n">
         <v>0.54</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" s="1">
+    <row r="18">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" t="n">
         <v>0.63</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="1">
+    <row r="19">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" t="n">
         <v>0.78</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" s="1">
+    <row r="20">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" t="n">
         <v>0.52</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="G24" t="s">
-        <v>20</v>
-      </c>
-      <c r="J24" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>